--- a/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
+++ b/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
@@ -14,22 +14,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={9f47dc6c-3a5b-42c6-bb01-1b6aefe21388}</author>
-    <author>tc={eafeb24c-37f8-43b3-ac3a-4455f64e24f4}</author>
+    <author>tc={bac1aef2-e572-4331-9846-54541794433c}</author>
+    <author>tc={ee38fc60-8bea-4d93-a370-98be4caaf866}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{9f47dc6c-3a5b-42c6-bb01-1b6aefe21388}" ref="C11">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	④全テーマ一覧の内容を全員で議論。
-Reply:
-	体制や、ゴールを全員で認識をそろえる
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{eafeb24c-37f8-43b3-ac3a-4455f64e24f4}" ref="A1">
+    <comment authorId="0" xr:uid="{bac1aef2-e572-4331-9846-54541794433c}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -41,6 +30,17 @@
 </t>
       </text>
     </comment>
+    <comment authorId="1" xr:uid="{ee38fc60-8bea-4d93-a370-98be4caaf866}" ref="C11">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	④全テーマ一覧の内容を全員で議論。
+Reply:
+	体制や、ゴールを全員で認識をそろえる
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -48,10 +48,20 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={4b796ff3-84c9-4239-ba23-58b2280b313f}</author>
+    <author>tc={1ed51b90-bef1-4715-a58a-7da7cf03809b}</author>
+    <author>tc={3fa9c7b7-4532-4534-86cc-ce1aa25c8934}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{4b796ff3-84c9-4239-ba23-58b2280b313f}" ref="B17">
+    <comment authorId="0" xr:uid="{1ed51b90-bef1-4715-a58a-7da7cf03809b}" ref="D10">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	大阪のように、分岐（解約完了できなかった場合）の対応を別途整理する必要はありそう。
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{3fa9c7b7-4532-4534-86cc-ce1aa25c8934}" ref="B17">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -65,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
   <si>
     <t>各事業テーマ｜推奨根拠・運用イメージ・トレードオフ</t>
   </si>
@@ -170,10 +180,7 @@
 コミュニティ</t>
   </si>
   <si>
-    <t>Shapenessを、
-仲間と共に
-生き続ける場所を
-つくる</t>
+    <t>コミュニティがShaperさんのものになるようにする</t>
   </si>
   <si>
     <t>【なぜこのテーマか】
@@ -203,7 +210,7 @@
   </si>
   <si>
     <t>自分の物語を言葉にして、
-Shapenessを
+『自分の軸』を
 見つける体験を
 設計しきる</t>
   </si>
@@ -287,6 +294,19 @@
     <t>観客・お客さん</t>
   </si>
   <si>
+    <t>大会の場で「また来たい・友人を連れてきたい」と自然に感じてい
+る</t>
+  </si>
+  <si>
+    <t>選手・観客・スポンサーの三者は連動しており、観客が「また来たい」と感じる大会は、スポンサーにとっても「協賛する価値がある場所」として映る。物販や演出の判断軸にもなる。</t>
+  </si>
+  <si>
+    <t>【物販・グッズの方向性を決めるとき】
+→「それは観客が会場で"また来たい"と感じる体験に繋がるか？」で判断する
+【会場演出・オペレーションを決めるとき】
+→「観客が選手の物語を感じられる設計になっているか？」を確認する</t>
+  </si>
+  <si>
     <t>協賛実行メンバー
 （しおんさん・ななこちゃん・鈴木）</t>
   </si>
@@ -307,16 +327,34 @@
 （柏・上板橋・大阪）</t>
   </si>
   <si>
-    <t>独立後も「Shape Fitと一緒にやってきてよかった」と思える状態で完了している</t>
+    <t>FC独立の完了・継続どちらの結果になっても、
+「Shape Fitと一緒にやってきてよかった」と
+感じている状態で次のステップに進んでいる</t>
   </si>
   <si>
-    <t>FC独立が「円満かつクリーン」であることは、Shape Fitのブランドと今後のコミュニティへの影響に直結する。関係性の毀損はSFFや口コミへの波及リスクがある。</t>
+    <t>FC独立が「円満かつクリーン」であることは、Shape Fitのブランドと今後のコミュニティへの影響に直結する。悪い関係性はSFFや口コミへの波及リスクがある。
+また、どんな結果になっても「やってきてよかった」と思えるよう、対応の一つひとつに意味を持たせながら進めることが、組織として長く続けるための判断軸になる。</t>
   </si>
   <si>
-    <t>【FC関連の対応依頼が来たとき】
-→「これは独立完了に必要か、それとも本部設計に必要か」で線引き
-【コミュニケーション設計時】
-→「この言い方はオーナーが納得感を持てるか？」を先に確認する</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">【FC関連の対応依頼が来たとき】
+→「これは独立完了に必要か、それとも本部設計に必要か」で線引きする
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>【コミュニケーション設計時】
+→「そっけなく・適当に見えていないか」を確認する。リソースをかけすぎる必要はないが、誠実さが伝わる対応を最低ラインにする</t>
+    </r>
   </si>
   <si>
     <r>
@@ -434,19 +472,39 @@
     </r>
   </si>
   <si>
-    <t>本部トレーナー2名</t>
+    <t>本店トレーナー2名</t>
   </si>
   <si>
-    <t>FC完了後に自分が担う役割を、自分の言葉で説明できている</t>
+    <t>FC完了後に自分が担う役割を、「ジム」と「MYS」の両方を踏まえた上で、自分の言葉で説明できている</t>
   </si>
   <si>
     <t>「本部を設計する」テーマは、トレーナー2名が自走できる人材になることが前提。到達基準が言語化されていなければ、育成の方向がバラバラになる。</t>
   </si>
   <si>
-    <t>【トレーナーへの業務アサイン時】
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">【トレーナーへの業務アサイン時】
 →「FC完了後の本部での活躍につながっているか」を基準にする
 【研修・フィードバック時】
-→「なぜその判断をしたか」を本人の言葉で説明させる機会をつくる</t>
+→「なぜその判断をしたか」を本人の言葉で説明させる機会をつくる
+【お客様対応・コミュニケーション時】
+→「この行動はShapeの理念と繋がっているか」を自分の言葉で説明できるか確認する
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>【役割の言語化は、本部から一方的に定義しない】
+→「あなたの役割はこれだ」と伝えるのではなく、2人と一緒に言葉にしていく場をつくる</t>
+    </r>
   </si>
   <si>
     <t>2人がどれだけ言語化できるかが大事
@@ -457,6 +515,37 @@
   </si>
   <si>
     <t>本店</t>
+  </si>
+  <si>
+    <t>今期は現在のパーソナルジムとして継続しながら、なーすけさんのオフラインセッションの実践の場として機能し、提供サービスの価値を自分たちの言葉で説明できている</t>
+  </si>
+  <si>
+    <t>MYSが本格ローンチするまでの移行期間、本店の存在意義が言語化されていないとトレーナーが迷う。
+「今ここで働いている意味」をメンバー全員が説明できる状態にしておくことが、来期以降の本部設計の土台になる。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">【トレーナーへの業務アサイン時】
+→「これは今期の本店の役割（パーソナルジム継続＋MYSオフラインの実践）に繋がっているか」で判断する
+【本店のサービスを振り返るとき】
+→「今提供しているサービスの価値を、自分の言葉で説明できるか」を確認する
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>【オフラインセッションの内容を整理するとき】
+→「この関わり方・問いは抽象化・型化できるか」という視点で記録に残す</t>
+    </r>
   </si>
   <si>
     <t>オフラインでテストしている内容について抽象化して、実施できるようになっていきたいな。</t>
@@ -494,7 +583,7 @@
   </si>
   <si>
     <t>自分の物語を言葉にして、
-Shapenessを見つける体験を
+『自分の軸』を見つける体験を
 設計しきる</t>
   </si>
   <si>
@@ -518,7 +607,7 @@
 （10〜11月〜）</t>
   </si>
   <si>
-    <t>プログラムの中で「自分の物語が動いた瞬間」を一つ、自分の言葉で話せている</t>
+    <t>「自己把握」から「自分軸の言語化」までの体験を通じて、続けられるに確信が出てる状態</t>
   </si>
   <si>
     <t>「自己効力感が上がる体験の設計」が機能したかどうかは、受講者が自分の変化を自分の言葉で語れるかで測られる。語れることが設計の正解の証拠になる。</t>
@@ -530,8 +619,8 @@
 →「この週が終わった時、受講者は何を言語化できているか」を先に決めてから中身を作る</t>
   </si>
   <si>
-    <t>自己把握→変容（ここの定義）まで
-MYSについてはどこまでやるのか？</t>
+    <t>MYSオンラインの担当範囲：自己把握→変容まで（合意済み）
+※SFF・SFCなど他事業との接続も含む全体CJMは別途整理予定</t>
   </si>
   <si>
     <t>実行メンバー</t>
@@ -573,10 +662,21 @@
     <r>
       <rPr>
         <rFont val="Arial"/>
+        <b/>
         <color rgb="FFFF0000"/>
         <sz val="9.0"/>
       </rPr>
-      <t>SFF後の有料化・拡大の土台になる。</t>
+      <t>SFF後の有料化・拡大の土台になる。
+特に「どれだけ熱量を持って語れるか」が、このコミュニティの質を決める。人数より熱量を先につくることで、来期の広がりが本物になる。</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
   </si>
   <si>
@@ -648,7 +748,10 @@
 →「任せてみる」機会を意図的にデザインし、反応を観察する</t>
   </si>
   <si>
-    <t>イベントのたびに「今日誰が語れるようになったか」を具体的な名前で言える</t>
+    <t>イベントごとに変化したメンバーを
+名前で把握しながら、
+16名の層構造（リーダー候補・フォロワー）の
+解像度を仮説として言語化し続けている</t>
   </si>
   <si>
     <t>テーマ「Shapenessを生き続ける場所」の進捗は数字ではなく、個別のメンバーの変化で測られる。実行メンバーが名前で語れることが「深める運営ができている」証拠になる。</t>
@@ -672,7 +775,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -768,6 +871,12 @@
     <font>
       <sz val="9.0"/>
       <color rgb="FF888888"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1174,7 +1283,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1286,6 +1395,12 @@
     <xf borderId="12" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="12" fillId="21" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1297,38 +1412,41 @@
     <xf borderId="11" fillId="23" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="12" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="12" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="12" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="12" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1336,10 +1454,10 @@
     <xf borderId="11" fillId="26" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="27" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="27" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="27" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="27" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="27" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1348,7 +1466,7 @@
     <xf borderId="12" fillId="27" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="28" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="28" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="28" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1360,10 +1478,10 @@
     <xf borderId="11" fillId="29" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="30" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="11" fillId="30" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="30" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="30" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="30" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1372,11 +1490,11 @@
     <xf borderId="12" fillId="30" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="31" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="31" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="31" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="12" fillId="31" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="31" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1387,10 +1505,10 @@
     <xf borderId="11" fillId="32" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="33" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="33" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="33" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="33" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1399,7 +1517,7 @@
     <xf borderId="12" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="34" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="34" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="12" fillId="34" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1408,10 +1526,19 @@
     <xf borderId="12" fillId="34" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="12" fillId="33" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="12" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="16" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="16" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1440,7 +1567,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="鈴木晴勝" id="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" providerId="google-sheets"/>
+  <x18tc:person displayName="鈴木晴勝" id="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1640,17 +1767,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" id="{eafeb24c-37f8-43b3-ac3a-4455f64e24f4}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{bac1aef2-e572-4331-9846-54541794433c}" done="0">
     <x18tc:text xml:space="preserve">16人の定義は？
 現段階は、2、3人</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" id="{767624e9-bbe5-41af-bccb-c562a2d7c0be}" parentId="{eafeb24c-37f8-43b3-ac3a-4455f64e24f4}">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{687fd886-9ca4-4ffe-9367-57384e062a6d}" parentId="{bac1aef2-e572-4331-9846-54541794433c}">
     <x18tc:text xml:space="preserve">今欲しいのはリーダーを支えるフォロワー</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" id="{9f47dc6c-3a5b-42c6-bb01-1b6aefe21388}" done="0">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{ee38fc60-8bea-4d93-a370-98be4caaf866}" done="0">
     <x18tc:text xml:space="preserve">④全テーマ一覧の内容を全員で議論。</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" id="{71699d2e-a021-4bb3-808c-263a1c58c4f3}" parentId="{9f47dc6c-3a5b-42c6-bb01-1b6aefe21388}">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{f0ab4ade-2102-4f2b-aff7-ad83d33451a3}" parentId="{ee38fc60-8bea-4d93-a370-98be4caaf866}">
     <x18tc:text xml:space="preserve">体制や、ゴールを全員で認識をそろえる</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1658,8 +1785,11 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B17" dT="2026-03-13T07:48:32.00" personId="{aad346bd-bc99-47e9-863f-426a3e40bd3d}" id="{4b796ff3-84c9-4239-ba23-58b2280b313f}" done="0">
+  <x18tc:threadedComment ref="B17" dT="2026-03-13T07:48:32.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{3fa9c7b7-4532-4534-86cc-ce1aa25c8934}" done="0">
     <x18tc:text xml:space="preserve">Shapenessではなく、もっと細分化して修正</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="D10" dT="2026-03-13T20:13:46.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{1ed51b90-bef1-4715-a58a-7da7cf03809b}" done="0">
+    <x18tc:text xml:space="preserve">大阪のように、分岐（解約完了できなかった場合）の対応を別途整理する必要はありそう。</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
 </file>
@@ -9851,294 +9981,306 @@
       <c r="C7" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="33"/>
-    </row>
-    <row r="8" ht="79.5" customHeight="1">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E7" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="F7" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="G7" s="33"/>
+    </row>
+    <row r="8" ht="79.5" customHeight="1">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42" t="s">
         <v>46</v>
       </c>
+      <c r="D8" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>49</v>
+      </c>
       <c r="G8" s="33"/>
     </row>
     <row r="9" ht="9.75" customHeight="1">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="10" ht="79.5" customHeight="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="47" t="s">
+      <c r="C10" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="D10" s="48" t="s">
         <v>51</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="79.5" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
-      <c r="C11" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="51" t="s">
+      <c r="C11" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="D11" s="52" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" ht="79.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="52" t="s">
+      <c r="E11" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="55" t="s">
+      <c r="F11" s="54" t="s">
         <v>58</v>
       </c>
+      <c r="G11" s="50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" ht="79.5" customHeight="1">
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" ht="9.75" customHeight="1">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
     </row>
     <row r="14" ht="79.5" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>59</v>
+      <c r="C14" s="61" t="s">
+        <v>65</v>
       </c>
-      <c r="D14" s="59" t="s">
-        <v>60</v>
+      <c r="D14" s="62" t="s">
+        <v>66</v>
       </c>
-      <c r="E14" s="60" t="s">
-        <v>61</v>
+      <c r="E14" s="63" t="s">
+        <v>67</v>
       </c>
-      <c r="F14" s="60" t="s">
-        <v>62</v>
+      <c r="F14" s="63" t="s">
+        <v>68</v>
       </c>
       <c r="G14" s="33"/>
     </row>
     <row r="15" ht="79.5" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="61" t="s">
-        <v>63</v>
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="64" t="s">
+        <v>69</v>
       </c>
-      <c r="D15" s="62" t="s">
-        <v>64</v>
+      <c r="D15" s="65" t="s">
+        <v>70</v>
       </c>
-      <c r="E15" s="63" t="s">
-        <v>65</v>
+      <c r="E15" s="66" t="s">
+        <v>71</v>
       </c>
-      <c r="F15" s="63" t="s">
-        <v>66</v>
+      <c r="F15" s="66" t="s">
+        <v>72</v>
       </c>
       <c r="G15" s="33"/>
     </row>
     <row r="16" ht="9.75" customHeight="1">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
     </row>
     <row r="17" ht="79.5" customHeight="1">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="65" t="s">
-        <v>67</v>
+      <c r="B17" s="68" t="s">
+        <v>73</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>68</v>
+      <c r="C17" s="69" t="s">
+        <v>74</v>
       </c>
-      <c r="D17" s="67" t="s">
-        <v>69</v>
+      <c r="D17" s="70" t="s">
+        <v>75</v>
       </c>
-      <c r="E17" s="68" t="s">
-        <v>70</v>
+      <c r="E17" s="71" t="s">
+        <v>76</v>
       </c>
-      <c r="F17" s="68" t="s">
-        <v>71</v>
+      <c r="F17" s="71" t="s">
+        <v>77</v>
       </c>
       <c r="G17" s="33"/>
     </row>
     <row r="18" ht="79.5" customHeight="1">
       <c r="A18" s="34"/>
       <c r="B18" s="34"/>
-      <c r="C18" s="69" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="48" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" ht="79.5" customHeight="1">
-      <c r="A19" s="39"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="67" t="s">
+      <c r="C18" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="D18" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="E18" s="74" t="s">
         <v>80</v>
       </c>
+      <c r="F18" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" ht="79.5" customHeight="1">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>86</v>
+      </c>
       <c r="G19" s="33"/>
     </row>
     <row r="20" ht="9.75" customHeight="1">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" ht="79.5" customHeight="1">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="74" t="s">
-        <v>81</v>
+      <c r="B21" s="77" t="s">
+        <v>87</v>
       </c>
-      <c r="C21" s="75" t="s">
-        <v>82</v>
+      <c r="C21" s="78" t="s">
+        <v>88</v>
       </c>
-      <c r="D21" s="76" t="s">
-        <v>83</v>
+      <c r="D21" s="79" t="s">
+        <v>89</v>
       </c>
-      <c r="E21" s="77" t="s">
-        <v>84</v>
+      <c r="E21" s="80" t="s">
+        <v>90</v>
       </c>
-      <c r="F21" s="77" t="s">
-        <v>85</v>
+      <c r="F21" s="80" t="s">
+        <v>91</v>
       </c>
-      <c r="G21" s="48" t="s">
-        <v>86</v>
+      <c r="G21" s="50" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="79.5" customHeight="1">
       <c r="A22" s="34"/>
       <c r="B22" s="34"/>
-      <c r="C22" s="78" t="s">
-        <v>87</v>
+      <c r="C22" s="81" t="s">
+        <v>93</v>
       </c>
-      <c r="D22" s="79" t="s">
-        <v>88</v>
+      <c r="D22" s="82" t="s">
+        <v>94</v>
       </c>
-      <c r="E22" s="80" t="s">
-        <v>89</v>
+      <c r="E22" s="83" t="s">
+        <v>95</v>
       </c>
-      <c r="F22" s="80" t="s">
-        <v>90</v>
+      <c r="F22" s="83" t="s">
+        <v>96</v>
       </c>
       <c r="G22" s="33"/>
     </row>
     <row r="23" ht="79.5" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="75" t="s">
-        <v>77</v>
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="78" t="s">
+        <v>83</v>
       </c>
-      <c r="D23" s="76" t="s">
-        <v>91</v>
+      <c r="D23" s="84" t="s">
+        <v>97</v>
       </c>
-      <c r="E23" s="81" t="s">
-        <v>92</v>
+      <c r="E23" s="85" t="s">
+        <v>98</v>
       </c>
-      <c r="F23" s="81" t="s">
-        <v>93</v>
+      <c r="F23" s="85" t="s">
+        <v>99</v>
       </c>
-      <c r="G23" s="48" t="s">
-        <v>94</v>
+      <c r="G23" s="50" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" ht="9.75" customHeight="1">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
     </row>
     <row r="25" ht="21.75" customHeight="1">
       <c r="A25" s="26"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87"/>
     </row>
     <row r="26" ht="84.0" customHeight="1">
-      <c r="B26" s="82" t="s">
-        <v>95</v>
+      <c r="B26" s="88" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -11118,13 +11260,12 @@
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="B21:B23"/>
-    <mergeCell ref="A25:G25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:A8"/>

--- a/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
+++ b/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
@@ -14,11 +14,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={bac1aef2-e572-4331-9846-54541794433c}</author>
-    <author>tc={ee38fc60-8bea-4d93-a370-98be4caaf866}</author>
+    <author>tc={78b6e04c-df78-499d-80c1-6ef17d3bb0ca}</author>
+    <author>tc={ee46d6a7-082a-46c4-af2a-eb23791b7c86}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{bac1aef2-e572-4331-9846-54541794433c}" ref="A1">
+    <comment authorId="0" xr:uid="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +30,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{ee38fc60-8bea-4d93-a370-98be4caaf866}" ref="C11">
+    <comment authorId="1" xr:uid="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}" ref="C11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,11 +48,11 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={1ed51b90-bef1-4715-a58a-7da7cf03809b}</author>
-    <author>tc={3fa9c7b7-4532-4534-86cc-ce1aa25c8934}</author>
+    <author>tc={39cb7c6d-d42b-464f-86e9-209f160bd9d1}</author>
+    <author>tc={7d134c46-edd2-4387-99f7-3cd87ac8fdf0}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{1ed51b90-bef1-4715-a58a-7da7cf03809b}" ref="D10">
+    <comment authorId="0" xr:uid="{39cb7c6d-d42b-464f-86e9-209f160bd9d1}" ref="D11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -61,7 +61,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{3fa9c7b7-4532-4534-86cc-ce1aa25c8934}" ref="B17">
+    <comment authorId="1" xr:uid="{7d134c46-edd2-4387-99f7-3cd87ac8fdf0}" ref="B18">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="106">
   <si>
     <t>各事業テーマ｜推奨根拠・運用イメージ・トレードオフ</t>
   </si>
@@ -291,6 +291,21 @@
 →「選手の物語が生まれる大会」を軸にした表現にする</t>
   </si>
   <si>
+    <t>Shaper（ボランティアスタッフ）</t>
+  </si>
+  <si>
+    <t>「SFFのスタッフとして関われてよかった」と自分の言葉で言えて、その熱量が選手やお客様に自然と伝わっている</t>
+  </si>
+  <si>
+    <t>顧客体験シートには「Shaperの元気な迎え入れ」が演出として設計されているが、それを安定再現する手段がない。品質はShaperの属人的な熱量に依存しており、マニュアルと意味づけの両方が必要</t>
+  </si>
+  <si>
+    <t>【Shaperシフト設計時】
+→「このマニュアルで初めての人が動けるか」を確認してから配置する
+【大会後振り返り時】
+→「よかったと言ってくれたShaperは何人いたか・何が理由か」を記録する</t>
+  </si>
+  <si>
     <t>観客・お客さん</t>
   </si>
   <si>
@@ -307,11 +322,28 @@
 →「観客が選手の物語を感じられる設計になっているか？」を確認する</t>
   </si>
   <si>
-    <t>協賛実行メンバー
-（しおんさん・ななこちゃん・鈴木）</t>
+    <t>協賛実行メンバー</t>
   </si>
   <si>
-    <t>自分たちが動いたプロセスが「来年誰でも使える型」として残ったと実感できている</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">自分たちが動いたプロセスが「来年誰でも使える型」として残ったと実感できている
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>大会後に選手・来場者・Shaperのアンケートデータが揃っており、「何が体験を動かしたか」を数字と言葉で来年のチームに引き継げる状態になっている</t>
+    </r>
   </si>
   <si>
     <t>テーマの核心は「個人の頑張り」ではなく「仕組みの確立」。3人の動きが型として言語化・記録されているかどうかが今期の真の成果物。</t>
@@ -775,7 +807,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -876,6 +908,12 @@
     <font>
       <b/>
       <sz val="10.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
@@ -1115,7 +1153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border/>
     <border>
       <left/>
@@ -1225,6 +1263,17 @@
       <top style="thin">
         <color rgb="FF888888"/>
       </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF888888"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF888888"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF888888"/>
       </bottom>
@@ -1276,6 +1325,11 @@
     <border>
       <left/>
       <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
     </border>
@@ -1283,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="95">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1364,82 +1418,98 @@
     <xf borderId="10" fillId="17" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="18" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="11" fillId="17" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="18" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="19" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="19" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="21" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="21" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="21" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="19" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="19" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="21" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="11" fillId="23" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="19" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="19" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="17" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="23" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="24" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="24" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1451,85 +1521,85 @@
     <xf borderId="0" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="26" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="26" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="27" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="27" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="27" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="27" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="27" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="27" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="27" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="27" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="28" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="28" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="28" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="28" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="28" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="28" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="29" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="29" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="30" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="30" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="30" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="30" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="30" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="30" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="30" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="30" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="31" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="31" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="31" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="31" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="31" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="31" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="30" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="30" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="32" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="32" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="33" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="33" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="34" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="34" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="34" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="34" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="34" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="34" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="16" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1538,7 +1608,7 @@
     <xf borderId="3" fillId="16" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1567,7 +1637,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="鈴木晴勝" id="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" providerId="google-sheets"/>
+  <x18tc:person displayName="鈴木晴勝" id="{59fe7fcb-557c-49ea-aafb-f0555080743b}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1767,17 +1837,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{bac1aef2-e572-4331-9846-54541794433c}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}" done="0">
     <x18tc:text xml:space="preserve">16人の定義は？
 現段階は、2、3人</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{687fd886-9ca4-4ffe-9367-57384e062a6d}" parentId="{bac1aef2-e572-4331-9846-54541794433c}">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{e68de60f-97ec-40f9-9a29-0227ac85a417}" parentId="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}">
     <x18tc:text xml:space="preserve">今欲しいのはリーダーを支えるフォロワー</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{ee38fc60-8bea-4d93-a370-98be4caaf866}" done="0">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}" done="0">
     <x18tc:text xml:space="preserve">④全テーマ一覧の内容を全員で議論。</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{f0ab4ade-2102-4f2b-aff7-ad83d33451a3}" parentId="{ee38fc60-8bea-4d93-a370-98be4caaf866}">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{886a0fa1-1ed9-4d28-aa1b-f976c2ffd1a9}" parentId="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}">
     <x18tc:text xml:space="preserve">体制や、ゴールを全員で認識をそろえる</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1785,10 +1855,10 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B17" dT="2026-03-13T07:48:32.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{3fa9c7b7-4532-4534-86cc-ce1aa25c8934}" done="0">
+  <x18tc:threadedComment ref="B18" dT="2026-03-13T07:48:32.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{7d134c46-edd2-4387-99f7-3cd87ac8fdf0}" done="0">
     <x18tc:text xml:space="preserve">Shapenessではなく、もっと細分化して修正</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="D10" dT="2026-03-13T20:13:46.00" personId="{f4b6b060-eda5-4116-91fb-4bd847c92efd}" id="{1ed51b90-bef1-4715-a58a-7da7cf03809b}" done="0">
+  <x18tc:threadedComment ref="D11" dT="2026-03-13T20:13:46.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{39cb7c6d-d42b-464f-86e9-209f160bd9d1}" done="0">
     <x18tc:text xml:space="preserve">大阪のように、分岐（解約完了できなかった場合）の対応を別途整理する必要はありそう。</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -9921,369 +9991,385 @@
       <c r="B4" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
     </row>
     <row r="6" ht="79.5" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35" t="s">
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
     </row>
     <row r="7" ht="79.5" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="38" t="s">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" ht="79.5" customHeight="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="33"/>
-    </row>
-    <row r="9" ht="9.75" customHeight="1">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-    </row>
-    <row r="10" ht="79.5" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" ht="79.5" customHeight="1">
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" ht="9.75" customHeight="1">
+      <c r="A10" s="49"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+    </row>
+    <row r="11" ht="79.5" customHeight="1">
+      <c r="A11" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B11" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="50" t="s">
+      <c r="C11" s="53" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" ht="79.5" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="51" t="s">
+      <c r="D11" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="E11" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="F11" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="G11" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="50" t="s">
+    </row>
+    <row r="12" ht="79.5" customHeight="1">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="57" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" ht="79.5" customHeight="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="55" t="s">
+      <c r="D12" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="E12" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="F12" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="G12" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="58" t="s">
+    </row>
+    <row r="13" ht="79.5" customHeight="1">
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="61" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" ht="9.75" customHeight="1">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-    </row>
-    <row r="14" ht="79.5" customHeight="1">
-      <c r="A14" s="59" t="s">
+      <c r="D13" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="9.75" customHeight="1">
+      <c r="A14" s="50"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+    </row>
+    <row r="15" ht="79.5" customHeight="1">
+      <c r="A15" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="60" t="s">
+      <c r="B15" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="33"/>
-    </row>
-    <row r="15" ht="79.5" customHeight="1">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="66" t="s">
+      <c r="E15" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="33"/>
-    </row>
-    <row r="16" ht="9.75" customHeight="1">
-      <c r="A16" s="44"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-    </row>
-    <row r="17" ht="79.5" customHeight="1">
-      <c r="A17" s="67" t="s">
+      <c r="G15" s="34"/>
+    </row>
+    <row r="16" ht="79.5" customHeight="1">
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" ht="9.75" customHeight="1">
+      <c r="A17" s="50"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+    </row>
+    <row r="18" ht="79.5" customHeight="1">
+      <c r="A18" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="71" t="s">
+      <c r="B18" s="74" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="33"/>
-    </row>
-    <row r="18" ht="79.5" customHeight="1">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="73" t="s">
+      <c r="D18" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="74" t="s">
+      <c r="E18" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="74" t="s">
+      <c r="F18" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="50" t="s">
+      <c r="G18" s="34"/>
+    </row>
+    <row r="19" ht="79.5" customHeight="1">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="78" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="19" ht="79.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="69" t="s">
+      <c r="D19" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="E19" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="F19" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="71" t="s">
+      <c r="G19" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="33"/>
-    </row>
-    <row r="20" ht="9.75" customHeight="1">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-    </row>
-    <row r="21" ht="79.5" customHeight="1">
-      <c r="A21" s="76" t="s">
+    </row>
+    <row r="20" ht="79.5" customHeight="1">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="34"/>
+    </row>
+    <row r="21" ht="9.75" customHeight="1">
+      <c r="A21" s="50"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+    </row>
+    <row r="22" ht="79.5" customHeight="1">
+      <c r="A22" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B22" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" ht="79.5" customHeight="1">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" ht="79.5" customHeight="1">
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="84" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="80" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" ht="79.5" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="81" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="33"/>
-    </row>
-    <row r="23" ht="79.5" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="84" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="85" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="85" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" ht="9.75" customHeight="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
-    </row>
-    <row r="26" ht="84.0" customHeight="1">
-      <c r="B26" s="88" t="s">
+      <c r="D24" s="90" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1"/>
+      <c r="E24" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" ht="9.75" customHeight="1">
+      <c r="A25" s="50"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+    </row>
+    <row r="26" ht="21.75" customHeight="1">
+      <c r="A26" s="26"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="93"/>
+    </row>
+    <row r="27" ht="84.0" customHeight="1">
+      <c r="B27" s="94" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
@@ -11259,20 +11345,21 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
     <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B15:B16"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>

--- a/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
+++ b/07.Shape/Shape_program_v2/24.曖昧な表現をなくす施策/outputs/今期テーマ_v2.xlsx
@@ -14,11 +14,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={78b6e04c-df78-499d-80c1-6ef17d3bb0ca}</author>
-    <author>tc={ee46d6a7-082a-46c4-af2a-eb23791b7c86}</author>
+    <author>tc={8b69ad0b-0dcd-41ef-b91d-210f91e0b93c}</author>
+    <author>tc={9ea79688-41ef-44f4-bc00-7bc11a409857}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}" ref="A1">
+    <comment authorId="0" xr:uid="{8b69ad0b-0dcd-41ef-b91d-210f91e0b93c}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -30,7 +30,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}" ref="C11">
+    <comment authorId="1" xr:uid="{9ea79688-41ef-44f4-bc00-7bc11a409857}" ref="C11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -48,11 +48,20 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={39cb7c6d-d42b-464f-86e9-209f160bd9d1}</author>
-    <author>tc={7d134c46-edd2-4387-99f7-3cd87ac8fdf0}</author>
+    <author>tc={103b51a9-51da-4653-bed8-48504caf5481}</author>
+    <author>tc={d4a6cbd6-9caf-4742-a879-0ccec2ad9b36}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{39cb7c6d-d42b-464f-86e9-209f160bd9d1}" ref="D11">
+    <comment authorId="0" xr:uid="{103b51a9-51da-4653-bed8-48504caf5481}" ref="B18">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Shapenessではなく、もっと細分化して修正
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{d4a6cbd6-9caf-4742-a879-0ccec2ad9b36}" ref="D11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -61,21 +70,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{7d134c46-edd2-4387-99f7-3cd87ac8fdf0}" ref="B18">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Shapenessではなく、もっと細分化して修正
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="105">
   <si>
     <t>各事業テーマ｜推奨根拠・運用イメージ・トレードオフ</t>
   </si>
@@ -282,7 +282,8 @@
     <t>この大会への出場が「自分の挑戦の物語の一部」だったと感じている</t>
   </si>
   <si>
-    <t>選手の体験・感情への共感はメンバーの行動動機の源泉。選手がこう感じている大会は、スポンサーにとっても「価値ある場所」に見える。両者は連動している。</t>
+    <t>選手の体験・感情への共感はメンバーの行動動機の源泉。
+選手が「自分の挑戦の物語の一部だった」と感じられる大会をつくることが、SFFの演出・設計のすべての出発点になる。</t>
   </si>
   <si>
     <t>【演出・当日設計の判断時】
@@ -313,9 +314,6 @@
 る</t>
   </si>
   <si>
-    <t>選手・観客・スポンサーの三者は連動しており、観客が「また来たい」と感じる大会は、スポンサーにとっても「協賛する価値がある場所」として映る。物販や演出の判断軸にもなる。</t>
-  </si>
-  <si>
     <t>【物販・グッズの方向性を決めるとき】
 →「それは観客が会場で"また来たい"と感じる体験に繋がるか？」で判断する
 【会場演出・オペレーションを決めるとき】
@@ -339,7 +337,7 @@
       <rPr>
         <rFont val="Arial"/>
         <b/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF1A1A1A"/>
         <sz val="10.0"/>
       </rPr>
       <t>大会後に選手・来場者・Shaperのアンケートデータが揃っており、「何が体験を動かしたか」を数字と言葉で来年のチームに引き継げる状態になっている</t>
@@ -906,13 +904,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9.0"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -921,6 +912,12 @@
       <b/>
       <sz val="10.0"/>
       <color rgb="FF1B4332"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1337,7 +1334,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="93">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1446,28 +1443,12 @@
     <xf borderId="13" fillId="21" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="19" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="19" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="19" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="13" fillId="21" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="19" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1477,18 +1458,28 @@
     <xf borderId="13" fillId="19" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="13" fillId="21" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="21" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" fillId="21" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="17" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="23" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="24" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="24" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="24" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="24" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1497,10 +1488,10 @@
     <xf borderId="13" fillId="20" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1509,10 +1500,10 @@
     <xf borderId="13" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="25" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="25" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="25" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="25" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1563,7 +1554,7 @@
     <xf borderId="13" fillId="31" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="31" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="31" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="31" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1596,7 +1587,7 @@
     <xf borderId="13" fillId="34" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="33" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="33" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="33" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1637,7 +1628,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="鈴木晴勝" id="{59fe7fcb-557c-49ea-aafb-f0555080743b}" providerId="google-sheets"/>
+  <x18tc:person displayName="鈴木晴勝" id="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1837,17 +1828,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:07.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{8b69ad0b-0dcd-41ef-b91d-210f91e0b93c}" done="0">
     <x18tc:text xml:space="preserve">16人の定義は？
 現段階は、2、3人</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{e68de60f-97ec-40f9-9a29-0227ac85a417}" parentId="{78b6e04c-df78-499d-80c1-6ef17d3bb0ca}">
+  <x18tc:threadedComment ref="A1" dT="2026-03-05T07:45:19.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{16f44a52-1ce3-4ada-85cd-094cfee41804}" parentId="{8b69ad0b-0dcd-41ef-b91d-210f91e0b93c}">
     <x18tc:text xml:space="preserve">今欲しいのはリーダーを支えるフォロワー</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}" done="0">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:17.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{9ea79688-41ef-44f4-bc00-7bc11a409857}" done="0">
     <x18tc:text xml:space="preserve">④全テーマ一覧の内容を全員で議論。</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{886a0fa1-1ed9-4d28-aa1b-f976c2ffd1a9}" parentId="{ee46d6a7-082a-46c4-af2a-eb23791b7c86}">
+  <x18tc:threadedComment ref="C11" dT="2026-03-05T07:46:30.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{24b7d73e-d68b-4cc5-a2ff-01e2effb943b}" parentId="{9ea79688-41ef-44f4-bc00-7bc11a409857}">
     <x18tc:text xml:space="preserve">体制や、ゴールを全員で認識をそろえる</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1855,10 +1846,10 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B18" dT="2026-03-13T07:48:32.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{7d134c46-edd2-4387-99f7-3cd87ac8fdf0}" done="0">
+  <x18tc:threadedComment ref="B18" dT="2026-03-13T07:48:32.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{103b51a9-51da-4653-bed8-48504caf5481}" done="0">
     <x18tc:text xml:space="preserve">Shapenessではなく、もっと細分化して修正</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="D11" dT="2026-03-13T20:13:46.00" personId="{59fe7fcb-557c-49ea-aafb-f0555080743b}" id="{39cb7c6d-d42b-464f-86e9-209f160bd9d1}" done="0">
+  <x18tc:threadedComment ref="D11" dT="2026-03-13T20:13:46.00" personId="{1b1ac3b8-5b93-46ac-87f6-b8cc2c06936c}" id="{d4a6cbd6-9caf-4742-a879-0ccec2ad9b36}" done="0">
     <x18tc:text xml:space="preserve">大阪のように、分岐（解約完了できなかった場合）の対応を別途整理する必要はありそう。</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -10040,7 +10031,7 @@
       <c r="E6" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="39" t="s">
         <v>41</v>
       </c>
       <c r="G6" s="34"/>
@@ -10048,16 +10039,16 @@
     <row r="7" ht="79.5" customHeight="1">
       <c r="A7" s="35"/>
       <c r="B7" s="35"/>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="42" t="s">
         <v>45</v>
       </c>
       <c r="G7" s="34"/>
@@ -10065,309 +10056,309 @@
     <row r="8" ht="79.5" customHeight="1">
       <c r="A8" s="35"/>
       <c r="B8" s="35"/>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" ht="79.5" customHeight="1">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="46" t="s">
+      <c r="D9" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="E9" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="F9" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="G9" s="34"/>
+    </row>
+    <row r="10" ht="9.75" customHeight="1">
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+    </row>
+    <row r="11" ht="79.5" customHeight="1">
+      <c r="A11" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" ht="9.75" customHeight="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-    </row>
-    <row r="11" ht="79.5" customHeight="1">
-      <c r="A11" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="53" t="s">
+      <c r="D11" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="E11" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="F11" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="G11" s="54" t="s">
         <v>57</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12" ht="79.5" customHeight="1">
       <c r="A12" s="35"/>
       <c r="B12" s="35"/>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="E12" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="F12" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="60" t="s">
+      <c r="G12" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="56" t="s">
+    </row>
+    <row r="13" ht="79.5" customHeight="1">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="59" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" ht="79.5" customHeight="1">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="61" t="s">
+      <c r="D13" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="E13" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="63" t="s">
+      <c r="F13" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="G13" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="64" t="s">
+    </row>
+    <row r="14" ht="9.75" customHeight="1">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+    </row>
+    <row r="15" ht="79.5" customHeight="1">
+      <c r="A15" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="65" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="14" ht="9.75" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-    </row>
-    <row r="15" ht="79.5" customHeight="1">
-      <c r="A15" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="67" t="s">
+      <c r="D15" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="68" t="s">
+      <c r="E15" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="69" t="s">
+      <c r="F15" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="69" t="s">
+      <c r="G15" s="34"/>
+    </row>
+    <row r="16" ht="79.5" customHeight="1">
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="70" t="s">
+      <c r="D16" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="E16" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="72" t="s">
+      <c r="F16" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" ht="9.75" customHeight="1">
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+    </row>
+    <row r="18" ht="79.5" customHeight="1">
+      <c r="A18" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="34"/>
-    </row>
-    <row r="17" ht="9.75" customHeight="1">
-      <c r="A17" s="50"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-    </row>
-    <row r="18" ht="79.5" customHeight="1">
-      <c r="A18" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="74" t="s">
+      <c r="C18" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="D18" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="E18" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="F18" s="75" t="s">
         <v>80</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>81</v>
       </c>
       <c r="G18" s="34"/>
     </row>
     <row r="19" ht="79.5" customHeight="1">
       <c r="A19" s="35"/>
       <c r="B19" s="35"/>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="76" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="79" t="s">
+      <c r="E19" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="80" t="s">
+      <c r="F19" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="80" t="s">
+      <c r="G19" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="56" t="s">
+    </row>
+    <row r="20" ht="79.5" customHeight="1">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="73" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="20" ht="79.5" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="75" t="s">
+      <c r="D20" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="E20" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="81" t="s">
+      <c r="F20" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="77" t="s">
+      <c r="G20" s="34"/>
+    </row>
+    <row r="21" ht="9.75" customHeight="1">
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+    </row>
+    <row r="22" ht="79.5" customHeight="1">
+      <c r="A22" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="34"/>
-    </row>
-    <row r="21" ht="9.75" customHeight="1">
-      <c r="A21" s="50"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-    </row>
-    <row r="22" ht="79.5" customHeight="1">
-      <c r="A22" s="82" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="83" t="s">
+      <c r="C22" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="D22" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="85" t="s">
+      <c r="E22" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="86" t="s">
+      <c r="F22" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="86" t="s">
+      <c r="G22" s="54" t="s">
         <v>95</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="23" ht="79.5" customHeight="1">
       <c r="A23" s="35"/>
       <c r="B23" s="35"/>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="E23" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="E23" s="89" t="s">
+      <c r="F23" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="89" t="s">
+      <c r="G23" s="34"/>
+    </row>
+    <row r="24" ht="79.5" customHeight="1">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="34"/>
-    </row>
-    <row r="24" ht="79.5" customHeight="1">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="84" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="90" t="s">
+      <c r="E24" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="91" t="s">
+      <c r="F24" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="91" t="s">
+      <c r="G24" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="56" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="25" ht="9.75" customHeight="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
     </row>
     <row r="26" ht="21.75" customHeight="1">
       <c r="A26" s="26"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="93"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="91"/>
     </row>
     <row r="27" ht="84.0" customHeight="1">
-      <c r="B27" s="94" t="s">
-        <v>105</v>
+      <c r="B27" s="92" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
